--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="3188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="3187">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202510230000</t>
+    <t>202512170000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-23T14:59:35-00:00</t>
+    <t>2025-12-17T14:37:59-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,6 +745,18 @@
     <t>Autre risque</t>
   </si>
   <si>
+    <t>GEN-092.01.25</t>
+  </si>
+  <si>
+    <t>Autre exposition</t>
+  </si>
+  <si>
+    <t>GEN-092.01.26</t>
+  </si>
+  <si>
+    <t>Autre complication</t>
+  </si>
+  <si>
     <t>GEN-092.02.01</t>
   </si>
   <si>
@@ -4489,7 +4501,7 @@
     <t>MED-508</t>
   </si>
   <si>
-    <t>Toubles digestifs justifiant une sonde gastrique</t>
+    <t>Troubles digestifs justifiant une sonde gastrique</t>
   </si>
   <si>
     <t>MED-511</t>
@@ -8335,6 +8347,48 @@
     <t>Evaluation CIM11</t>
   </si>
   <si>
+    <t>MED-1330</t>
+  </si>
+  <si>
+    <t>Etat de conscience inconnu</t>
+  </si>
+  <si>
+    <t>MED-1331</t>
+  </si>
+  <si>
+    <t>allergie à une substance</t>
+  </si>
+  <si>
+    <t>MED-1332</t>
+  </si>
+  <si>
+    <t>hypersensibilité non allergique à une substance</t>
+  </si>
+  <si>
+    <t>MED-1333</t>
+  </si>
+  <si>
+    <t>intolérance à un agent environnemental</t>
+  </si>
+  <si>
+    <t>MED-1334</t>
+  </si>
+  <si>
+    <t>mésusage ou d’un usage détourné</t>
+  </si>
+  <si>
+    <t>MED-1335</t>
+  </si>
+  <si>
+    <t>Médicament augmentant l’INR</t>
+  </si>
+  <si>
+    <t>MED-1336</t>
+  </si>
+  <si>
+    <t>Médicament diminuant l’INR</t>
+  </si>
+  <si>
     <t>ORG-001</t>
   </si>
   <si>
@@ -8503,511 +8557,454 @@
     <t>Protocole de recherche</t>
   </si>
   <si>
-    <t>ORG-054</t>
+    <t>ORG-063</t>
+  </si>
+  <si>
+    <t>Acte ou intervention prévu ou à programmer</t>
+  </si>
+  <si>
+    <t>ORG-064</t>
+  </si>
+  <si>
+    <t>Demande d'examen ou de suivi</t>
+  </si>
+  <si>
+    <t>ORG-065</t>
+  </si>
+  <si>
+    <t>Suites à donner d'ordre médico-social</t>
+  </si>
+  <si>
+    <t>ORG-070</t>
+  </si>
+  <si>
+    <t>Modalité d'entrée</t>
+  </si>
+  <si>
+    <t>ORG-074</t>
+  </si>
+  <si>
+    <t>Modalité de sortie</t>
+  </si>
+  <si>
+    <t>ORG-075</t>
+  </si>
+  <si>
+    <t>Activité professionnelle</t>
+  </si>
+  <si>
+    <t>ORG-077</t>
+  </si>
+  <si>
+    <t>Hospitalisation (y compris à domicile)</t>
+  </si>
+  <si>
+    <t>ORG-079</t>
+  </si>
+  <si>
+    <t>Nombre total d'échographies</t>
+  </si>
+  <si>
+    <t>ORG-080</t>
+  </si>
+  <si>
+    <t>Echographie morphologique</t>
+  </si>
+  <si>
+    <t>ORG-081</t>
+  </si>
+  <si>
+    <t>Type de transfert</t>
+  </si>
+  <si>
+    <t>ORG-085</t>
+  </si>
+  <si>
+    <t>Demande de surveillance médicale particulière</t>
+  </si>
+  <si>
+    <t>ORG-086</t>
+  </si>
+  <si>
+    <t>Motif d'hospitalisation</t>
+  </si>
+  <si>
+    <t>ORG-087</t>
+  </si>
+  <si>
+    <t>Nombre d'hospitalisations</t>
+  </si>
+  <si>
+    <t>ORG-088</t>
+  </si>
+  <si>
+    <t>Nombre d'hospitalisations depuis le 9ème mois</t>
+  </si>
+  <si>
+    <t>ORG-089</t>
+  </si>
+  <si>
+    <t>Nombre d'hospitalisations après le 9ème mois</t>
+  </si>
+  <si>
+    <t>ORG-092</t>
+  </si>
+  <si>
+    <t>Nombre d'hospitalisations en période néonatale</t>
+  </si>
+  <si>
+    <t>ORG-094</t>
+  </si>
+  <si>
+    <t>Nombre d'hospitalisations après la période néonatale</t>
+  </si>
+  <si>
+    <t>ORG-095</t>
+  </si>
+  <si>
+    <t>Type morphologique</t>
+  </si>
+  <si>
+    <t>ORG-097</t>
+  </si>
+  <si>
+    <t>Correspondant</t>
+  </si>
+  <si>
+    <t>ORG-098</t>
+  </si>
+  <si>
+    <t>Lieu du transfert</t>
+  </si>
+  <si>
+    <t>ORG-099</t>
+  </si>
+  <si>
+    <t>Profession</t>
+  </si>
+  <si>
+    <t>ORG-102</t>
+  </si>
+  <si>
+    <t>SSR spécialisé neuro</t>
+  </si>
+  <si>
+    <t>ORG-103</t>
+  </si>
+  <si>
+    <t>SSR spécialisé gériatrie</t>
+  </si>
+  <si>
+    <t>ORG-104</t>
+  </si>
+  <si>
+    <t>SSR polyvalent</t>
+  </si>
+  <si>
+    <t>ORG-114</t>
+  </si>
+  <si>
+    <t>Proposition de traitement (dont ajustement et surveillance)</t>
+  </si>
+  <si>
+    <t>ORG-115</t>
+  </si>
+  <si>
+    <t>Recours</t>
+  </si>
+  <si>
+    <t>ORG-116</t>
+  </si>
+  <si>
+    <t>Pédiatrie</t>
+  </si>
+  <si>
+    <t>ORG-117</t>
+  </si>
+  <si>
+    <t>RCP Appareil - Organes</t>
+  </si>
+  <si>
+    <t>ORG-118</t>
+  </si>
+  <si>
+    <t>Appareil concerné</t>
+  </si>
+  <si>
+    <t>ORG-119</t>
+  </si>
+  <si>
+    <t>Organe</t>
+  </si>
+  <si>
+    <t>ORG-120</t>
+  </si>
+  <si>
+    <t>Passage en RCP recours</t>
+  </si>
+  <si>
+    <t>ORG-121</t>
+  </si>
+  <si>
+    <t>Evaluation Oncogériatrique</t>
+  </si>
+  <si>
+    <t>ORG-122</t>
+  </si>
+  <si>
+    <t>Consultation génétique</t>
+  </si>
+  <si>
+    <t>ORG-125</t>
+  </si>
+  <si>
+    <t>Quorum RCP</t>
+  </si>
+  <si>
+    <t>ORG-126</t>
+  </si>
+  <si>
+    <t>Quorum atteint</t>
+  </si>
+  <si>
+    <t>ORG-127</t>
+  </si>
+  <si>
+    <t>Statut du cas présenté</t>
+  </si>
+  <si>
+    <t>ORG-128</t>
+  </si>
+  <si>
+    <t>Cas enregistré</t>
+  </si>
+  <si>
+    <t>ORG-129</t>
+  </si>
+  <si>
+    <t>Oncogénétique</t>
+  </si>
+  <si>
+    <t>ORG-130</t>
+  </si>
+  <si>
+    <t>Oncogériatrie</t>
+  </si>
+  <si>
+    <t>ORG-132</t>
+  </si>
+  <si>
+    <t>RCP Transversale et de soins de support</t>
+  </si>
+  <si>
+    <t>ORG-133</t>
+  </si>
+  <si>
+    <t>Quorum non atteint</t>
+  </si>
+  <si>
+    <t>ORG-134</t>
+  </si>
+  <si>
+    <t>Cas discuté</t>
+  </si>
+  <si>
+    <t>ORG-135</t>
+  </si>
+  <si>
+    <t>Session RCP et inscription</t>
+  </si>
+  <si>
+    <t>ORG-136</t>
+  </si>
+  <si>
+    <t>Médecin coordonateur de session</t>
+  </si>
+  <si>
+    <t>ORG-137</t>
+  </si>
+  <si>
+    <t>PS participant à la session de RCP</t>
+  </si>
+  <si>
+    <t>ORG-138</t>
+  </si>
+  <si>
+    <t>Traitement/Soins</t>
+  </si>
+  <si>
+    <t>ORG-141</t>
+  </si>
+  <si>
+    <t>Unité Kangourou</t>
+  </si>
+  <si>
+    <t>ORG-143</t>
+  </si>
+  <si>
+    <t>Réanimation/soins intentifs</t>
+  </si>
+  <si>
+    <t>ORG-145</t>
+  </si>
+  <si>
+    <t>Service réadaptation</t>
+  </si>
+  <si>
+    <t>ORG-146</t>
+  </si>
+  <si>
+    <t>Psychiatrie</t>
+  </si>
+  <si>
+    <t>ORG-147</t>
+  </si>
+  <si>
+    <t>Établissement de santé de moyen ou long séjour</t>
+  </si>
+  <si>
+    <t>ORG-148</t>
+  </si>
+  <si>
+    <t>Établissement ou service de soins de suite</t>
+  </si>
+  <si>
+    <t>ORG-149</t>
+  </si>
+  <si>
+    <t>Établissement d’hébergement de personnes handicapées</t>
+  </si>
+  <si>
+    <t>ORG-150</t>
+  </si>
+  <si>
+    <t>Institution psychiatrique</t>
+  </si>
+  <si>
+    <t>ORG-151</t>
+  </si>
+  <si>
+    <t>Prison</t>
+  </si>
+  <si>
+    <t>ORG-152</t>
+  </si>
+  <si>
+    <t>Police</t>
+  </si>
+  <si>
+    <t>ORG-153</t>
+  </si>
+  <si>
+    <t>SAMU, SMUR terrestre</t>
+  </si>
+  <si>
+    <t>ORG-154</t>
+  </si>
+  <si>
+    <t>Ambulance publique</t>
+  </si>
+  <si>
+    <t>ORG-155</t>
+  </si>
+  <si>
+    <t>Ambulance privée</t>
+  </si>
+  <si>
+    <t>ORG-156</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>ORG-157</t>
+  </si>
+  <si>
+    <t>Moyens personnels</t>
+  </si>
+  <si>
+    <t>ORG-158</t>
+  </si>
+  <si>
+    <t>SAMU, SMUR Hélicoptère</t>
+  </si>
+  <si>
+    <t>ORG-159</t>
+  </si>
+  <si>
+    <t>Pompier</t>
+  </si>
+  <si>
+    <t>ORG-160</t>
+  </si>
+  <si>
+    <t>VSL</t>
+  </si>
+  <si>
+    <t>ORG-162</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>ORG-163</t>
+  </si>
+  <si>
+    <t>Consultation de spécialité</t>
+  </si>
+  <si>
+    <t>ORG-165</t>
+  </si>
+  <si>
+    <t>Séjour de répit</t>
+  </si>
+  <si>
+    <t>ORG-170</t>
+  </si>
+  <si>
+    <t>Site Maladie rare</t>
+  </si>
+  <si>
+    <t>ORG-171</t>
+  </si>
+  <si>
+    <t>Prise en charge des conséquences des tumeurs cérébrales et de leurs traitements</t>
+  </si>
+  <si>
+    <t>ORG-172</t>
+  </si>
+  <si>
+    <t>Exécutant</t>
+  </si>
+  <si>
+    <t>ORG-173</t>
+  </si>
+  <si>
+    <t>Projet de grossesse</t>
+  </si>
+  <si>
+    <t>ORG-174</t>
+  </si>
+  <si>
+    <t>Continuité de la scolarité</t>
+  </si>
+  <si>
+    <t>ORG-175</t>
+  </si>
+  <si>
+    <t>Activité physique adaptée</t>
+  </si>
+  <si>
+    <t>ORG-176</t>
+  </si>
+  <si>
+    <t>Conseil d’hygiène de vie</t>
+  </si>
+  <si>
+    <t>ORG-177</t>
   </si>
   <si>
     <t>Établissement de santé de référence</t>
-  </si>
-  <si>
-    <t>ORG-055</t>
-  </si>
-  <si>
-    <t>Centre d'hébergement</t>
-  </si>
-  <si>
-    <t>ORG-056</t>
-  </si>
-  <si>
-    <t>Structure(s) de coordination ville-hôpital</t>
-  </si>
-  <si>
-    <t>ORG-057</t>
-  </si>
-  <si>
-    <t>Organisme social et de maintien dans l'emploi</t>
-  </si>
-  <si>
-    <t>ORG-059</t>
-  </si>
-  <si>
-    <t>Lieu d'administration</t>
-  </si>
-  <si>
-    <t>ORG-060</t>
-  </si>
-  <si>
-    <t>Lieu de prise en charge en oncogératrie</t>
-  </si>
-  <si>
-    <t>ORG-061</t>
-  </si>
-  <si>
-    <t>Lieu des mesures de préservation de la fertilité</t>
-  </si>
-  <si>
-    <t>ORG-062</t>
-  </si>
-  <si>
-    <t>Structure(s) de soutien et d'information</t>
-  </si>
-  <si>
-    <t>ORG-063</t>
-  </si>
-  <si>
-    <t>Acte ou intervention prévu ou à programmer</t>
-  </si>
-  <si>
-    <t>ORG-064</t>
-  </si>
-  <si>
-    <t>Demande d'examen ou de suivi</t>
-  </si>
-  <si>
-    <t>ORG-065</t>
-  </si>
-  <si>
-    <t>Suites à donner d'ordre médico-social</t>
-  </si>
-  <si>
-    <t>ORG-070</t>
-  </si>
-  <si>
-    <t>Modalité d'entrée</t>
-  </si>
-  <si>
-    <t>ORG-074</t>
-  </si>
-  <si>
-    <t>Modalité de sortie</t>
-  </si>
-  <si>
-    <t>ORG-075</t>
-  </si>
-  <si>
-    <t>Activité professionnelle</t>
-  </si>
-  <si>
-    <t>ORG-077</t>
-  </si>
-  <si>
-    <t>Hospitalisation (y compris à domicile)</t>
-  </si>
-  <si>
-    <t>ORG-079</t>
-  </si>
-  <si>
-    <t>Nombre total d'échographies</t>
-  </si>
-  <si>
-    <t>ORG-080</t>
-  </si>
-  <si>
-    <t>Echographie morphologique</t>
-  </si>
-  <si>
-    <t>ORG-081</t>
-  </si>
-  <si>
-    <t>Type de transfert</t>
-  </si>
-  <si>
-    <t>ORG-085</t>
-  </si>
-  <si>
-    <t>Demande de surveillance médicale particulière</t>
-  </si>
-  <si>
-    <t>ORG-086</t>
-  </si>
-  <si>
-    <t>Motif d'hospitalisation</t>
-  </si>
-  <si>
-    <t>ORG-087</t>
-  </si>
-  <si>
-    <t>Nombre d'hospitalisations</t>
-  </si>
-  <si>
-    <t>ORG-088</t>
-  </si>
-  <si>
-    <t>Nombre d'hospitalisations depuis le 9ème mois</t>
-  </si>
-  <si>
-    <t>ORG-089</t>
-  </si>
-  <si>
-    <t>Nombre d'hospitalisations après le 9ème mois</t>
-  </si>
-  <si>
-    <t>ORG-092</t>
-  </si>
-  <si>
-    <t>Nombre d'hospitalisations en période néonatale</t>
-  </si>
-  <si>
-    <t>ORG-094</t>
-  </si>
-  <si>
-    <t>Nombre d'hospitalisations après la période néonatale</t>
-  </si>
-  <si>
-    <t>ORG-095</t>
-  </si>
-  <si>
-    <t>Type morphologique</t>
-  </si>
-  <si>
-    <t>ORG-097</t>
-  </si>
-  <si>
-    <t>Correspondant</t>
-  </si>
-  <si>
-    <t>ORG-098</t>
-  </si>
-  <si>
-    <t>Lieu du transfert</t>
-  </si>
-  <si>
-    <t>ORG-099</t>
-  </si>
-  <si>
-    <t>Profession</t>
-  </si>
-  <si>
-    <t>ORG-102</t>
-  </si>
-  <si>
-    <t>SSR spécialisé neuro</t>
-  </si>
-  <si>
-    <t>ORG-103</t>
-  </si>
-  <si>
-    <t>SSR spécialisé gériatrie</t>
-  </si>
-  <si>
-    <t>ORG-104</t>
-  </si>
-  <si>
-    <t>SSR polyvalent</t>
-  </si>
-  <si>
-    <t>ORG-109</t>
-  </si>
-  <si>
-    <t>Caisse d'assurance de retraite et santé au travail (CARSAT)</t>
-  </si>
-  <si>
-    <t>ORG-110</t>
-  </si>
-  <si>
-    <t>Service d'appui au maintien dans l'emploi des travailleurs handicapés (SAMETH)</t>
-  </si>
-  <si>
-    <t>ORG-114</t>
-  </si>
-  <si>
-    <t>Proposition de traitement (dont ajustement et surveillance)</t>
-  </si>
-  <si>
-    <t>ORG-115</t>
-  </si>
-  <si>
-    <t>Recours</t>
-  </si>
-  <si>
-    <t>ORG-116</t>
-  </si>
-  <si>
-    <t>Pédiatrie</t>
-  </si>
-  <si>
-    <t>ORG-117</t>
-  </si>
-  <si>
-    <t>RCP Appareil - Organes</t>
-  </si>
-  <si>
-    <t>ORG-118</t>
-  </si>
-  <si>
-    <t>Appareil concerné</t>
-  </si>
-  <si>
-    <t>ORG-119</t>
-  </si>
-  <si>
-    <t>Organe</t>
-  </si>
-  <si>
-    <t>ORG-120</t>
-  </si>
-  <si>
-    <t>Passage en RCP recours</t>
-  </si>
-  <si>
-    <t>ORG-121</t>
-  </si>
-  <si>
-    <t>Evaluation Oncogériatrique</t>
-  </si>
-  <si>
-    <t>ORG-122</t>
-  </si>
-  <si>
-    <t>Consultation génétique</t>
-  </si>
-  <si>
-    <t>ORG-125</t>
-  </si>
-  <si>
-    <t>Quorum RCP</t>
-  </si>
-  <si>
-    <t>ORG-126</t>
-  </si>
-  <si>
-    <t>Quorum atteint</t>
-  </si>
-  <si>
-    <t>ORG-127</t>
-  </si>
-  <si>
-    <t>Statut du cas présenté</t>
-  </si>
-  <si>
-    <t>ORG-128</t>
-  </si>
-  <si>
-    <t>Cas enregistré</t>
-  </si>
-  <si>
-    <t>ORG-129</t>
-  </si>
-  <si>
-    <t>Oncogénétique</t>
-  </si>
-  <si>
-    <t>ORG-130</t>
-  </si>
-  <si>
-    <t>Oncogériatrie</t>
-  </si>
-  <si>
-    <t>ORG-132</t>
-  </si>
-  <si>
-    <t>RCP Transversale et de soins de support</t>
-  </si>
-  <si>
-    <t>ORG-133</t>
-  </si>
-  <si>
-    <t>Quorum non atteint</t>
-  </si>
-  <si>
-    <t>ORG-134</t>
-  </si>
-  <si>
-    <t>Cas discuté</t>
-  </si>
-  <si>
-    <t>ORG-135</t>
-  </si>
-  <si>
-    <t>Session RCP et inscription</t>
-  </si>
-  <si>
-    <t>ORG-136</t>
-  </si>
-  <si>
-    <t>Médecin coordonateur de session</t>
-  </si>
-  <si>
-    <t>ORG-137</t>
-  </si>
-  <si>
-    <t>PS participant à la session de RCP</t>
-  </si>
-  <si>
-    <t>ORG-138</t>
-  </si>
-  <si>
-    <t>Traitement/Soins</t>
-  </si>
-  <si>
-    <t>ORG-141</t>
-  </si>
-  <si>
-    <t>Unité Kangourou</t>
-  </si>
-  <si>
-    <t>ORG-143</t>
-  </si>
-  <si>
-    <t>Réanimation/soins intentifs</t>
-  </si>
-  <si>
-    <t>ORG-145</t>
-  </si>
-  <si>
-    <t>Service réadaptation</t>
-  </si>
-  <si>
-    <t>ORG-146</t>
-  </si>
-  <si>
-    <t>Psychiatrie</t>
-  </si>
-  <si>
-    <t>ORG-147</t>
-  </si>
-  <si>
-    <t>Établissement de santé de moyen ou long séjour</t>
-  </si>
-  <si>
-    <t>ORG-148</t>
-  </si>
-  <si>
-    <t>Établissement ou service de soins de suite</t>
-  </si>
-  <si>
-    <t>ORG-149</t>
-  </si>
-  <si>
-    <t>Établissement d’hébergement de personnes handicapées</t>
-  </si>
-  <si>
-    <t>ORG-150</t>
-  </si>
-  <si>
-    <t>Institution psychiatrique</t>
-  </si>
-  <si>
-    <t>ORG-151</t>
-  </si>
-  <si>
-    <t>Prison</t>
-  </si>
-  <si>
-    <t>ORG-152</t>
-  </si>
-  <si>
-    <t>Police</t>
-  </si>
-  <si>
-    <t>ORG-153</t>
-  </si>
-  <si>
-    <t>SAMU, SMUR terrestre</t>
-  </si>
-  <si>
-    <t>ORG-154</t>
-  </si>
-  <si>
-    <t>Ambulance publique</t>
-  </si>
-  <si>
-    <t>ORG-155</t>
-  </si>
-  <si>
-    <t>Ambulance privée</t>
-  </si>
-  <si>
-    <t>ORG-156</t>
-  </si>
-  <si>
-    <t>Taxi</t>
-  </si>
-  <si>
-    <t>ORG-157</t>
-  </si>
-  <si>
-    <t>Moyens personnels</t>
-  </si>
-  <si>
-    <t>ORG-158</t>
-  </si>
-  <si>
-    <t>SAMU, SMUR Hélicoptère</t>
-  </si>
-  <si>
-    <t>ORG-159</t>
-  </si>
-  <si>
-    <t>Pompier</t>
-  </si>
-  <si>
-    <t>ORG-160</t>
-  </si>
-  <si>
-    <t>VSL</t>
-  </si>
-  <si>
-    <t>ORG-162</t>
-  </si>
-  <si>
-    <t>MCO</t>
-  </si>
-  <si>
-    <t>ORG-163</t>
-  </si>
-  <si>
-    <t>Consultation de spécialité</t>
-  </si>
-  <si>
-    <t>ORG-165</t>
-  </si>
-  <si>
-    <t>Séjour de répit</t>
-  </si>
-  <si>
-    <t>ORG-170</t>
-  </si>
-  <si>
-    <t>Site Maladie rare</t>
-  </si>
-  <si>
-    <t>ORG-171</t>
-  </si>
-  <si>
-    <t>Prise en charge des conséquences des tumeurs cérébrales et de leurs traitements</t>
-  </si>
-  <si>
-    <t>ORG-172</t>
-  </si>
-  <si>
-    <t>Exécutant</t>
-  </si>
-  <si>
-    <t>ORG-173</t>
-  </si>
-  <si>
-    <t>Projet de grossesse</t>
-  </si>
-  <si>
-    <t>ORG-174</t>
-  </si>
-  <si>
-    <t>Continuité de la scolarité</t>
-  </si>
-  <si>
-    <t>ORG-175</t>
-  </si>
-  <si>
-    <t>Activité physique adaptée</t>
-  </si>
-  <si>
-    <t>ORG-176</t>
-  </si>
-  <si>
-    <t>Conseil d’hygiène de vie</t>
-  </si>
-  <si>
-    <t>ORG-177</t>
   </si>
   <si>
     <t>ORG-178</t>
@@ -9971,7 +9968,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1574"/>
+  <dimension ref="A1:D1573"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -12408,7 +12405,7 @@
         <v>457</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>35</v>
+        <v>458</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -12417,10 +12414,10 @@
         <v>55</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -12429,10 +12426,10 @@
         <v>55</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>461</v>
+        <v>35</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -14232,7 +14229,7 @@
         <v>760</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>91</v>
+        <v>761</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -14241,10 +14238,10 @@
         <v>55</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -14253,10 +14250,10 @@
         <v>55</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>764</v>
+        <v>91</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -16392,7 +16389,7 @@
         <v>1119</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>198</v>
+        <v>1120</v>
       </c>
       <c r="D535" s="2"/>
     </row>
@@ -16401,10 +16398,10 @@
         <v>55</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D536" s="2"/>
     </row>
@@ -16413,10 +16410,10 @@
         <v>55</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1123</v>
+        <v>198</v>
       </c>
       <c r="D537" s="2"/>
     </row>
@@ -21024,7 +21021,7 @@
         <v>1890</v>
       </c>
       <c r="C921" t="s" s="2">
-        <v>559</v>
+        <v>1891</v>
       </c>
       <c r="D921" s="2"/>
     </row>
@@ -21033,10 +21030,10 @@
         <v>55</v>
       </c>
       <c r="B922" t="s" s="2">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C922" t="s" s="2">
-        <v>561</v>
+        <v>1893</v>
       </c>
       <c r="D922" s="2"/>
     </row>
@@ -21045,10 +21042,10 @@
         <v>55</v>
       </c>
       <c r="B923" t="s" s="2">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="C923" t="s" s="2">
-        <v>1893</v>
+        <v>563</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -21057,10 +21054,10 @@
         <v>55</v>
       </c>
       <c r="B924" t="s" s="2">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="C924" t="s" s="2">
-        <v>1895</v>
+        <v>565</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -21564,7 +21561,7 @@
         <v>1978</v>
       </c>
       <c r="C966" t="s" s="2">
-        <v>1933</v>
+        <v>1979</v>
       </c>
       <c r="D966" s="2"/>
     </row>
@@ -21573,10 +21570,10 @@
         <v>55</v>
       </c>
       <c r="B967" t="s" s="2">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="C967" t="s" s="2">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="D967" s="2"/>
     </row>
@@ -21585,10 +21582,10 @@
         <v>55</v>
       </c>
       <c r="B968" t="s" s="2">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C968" t="s" s="2">
-        <v>1982</v>
+        <v>1937</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -23136,7 +23133,7 @@
         <v>2239</v>
       </c>
       <c r="C1097" t="s" s="2">
-        <v>2188</v>
+        <v>2240</v>
       </c>
       <c r="D1097" s="2"/>
     </row>
@@ -23145,10 +23142,10 @@
         <v>55</v>
       </c>
       <c r="B1098" t="s" s="2">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="C1098" t="s" s="2">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="D1098" s="2"/>
     </row>
@@ -23157,10 +23154,10 @@
         <v>55</v>
       </c>
       <c r="B1099" t="s" s="2">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="C1099" t="s" s="2">
-        <v>2243</v>
+        <v>2192</v>
       </c>
       <c r="D1099" s="2"/>
     </row>
@@ -25416,7 +25413,7 @@
         <v>2618</v>
       </c>
       <c r="C1287" t="s" s="2">
-        <v>2571</v>
+        <v>2619</v>
       </c>
       <c r="D1287" s="2"/>
     </row>
@@ -25425,10 +25422,10 @@
         <v>55</v>
       </c>
       <c r="B1288" t="s" s="2">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="C1288" t="s" s="2">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="D1288" s="2"/>
     </row>
@@ -25437,10 +25434,10 @@
         <v>55</v>
       </c>
       <c r="B1289" t="s" s="2">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="C1289" t="s" s="2">
-        <v>2622</v>
+        <v>2575</v>
       </c>
       <c r="D1289" s="2"/>
     </row>
@@ -25872,7 +25869,7 @@
         <v>2693</v>
       </c>
       <c r="C1325" t="s" s="2">
-        <v>292</v>
+        <v>2694</v>
       </c>
       <c r="D1325" s="2"/>
     </row>
@@ -25881,10 +25878,10 @@
         <v>55</v>
       </c>
       <c r="B1326" t="s" s="2">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="C1326" t="s" s="2">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="D1326" s="2"/>
     </row>
@@ -25893,10 +25890,10 @@
         <v>55</v>
       </c>
       <c r="B1327" t="s" s="2">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="C1327" t="s" s="2">
-        <v>2697</v>
+        <v>296</v>
       </c>
       <c r="D1327" s="2"/>
     </row>
@@ -26028,7 +26025,7 @@
         <v>2718</v>
       </c>
       <c r="C1338" t="s" s="2">
-        <v>57</v>
+        <v>2719</v>
       </c>
       <c r="D1338" s="2"/>
     </row>
@@ -26037,10 +26034,10 @@
         <v>55</v>
       </c>
       <c r="B1339" t="s" s="2">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="C1339" t="s" s="2">
-        <v>59</v>
+        <v>2721</v>
       </c>
       <c r="D1339" s="2"/>
     </row>
@@ -26049,10 +26046,10 @@
         <v>55</v>
       </c>
       <c r="B1340" t="s" s="2">
-        <v>2720</v>
+        <v>2722</v>
       </c>
       <c r="C1340" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D1340" s="2"/>
     </row>
@@ -26061,10 +26058,10 @@
         <v>55</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>2721</v>
+        <v>2723</v>
       </c>
       <c r="C1341" t="s" s="2">
-        <v>2722</v>
+        <v>59</v>
       </c>
       <c r="D1341" s="2"/>
     </row>
@@ -26073,10 +26070,10 @@
         <v>55</v>
       </c>
       <c r="B1342" t="s" s="2">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="C1342" t="s" s="2">
-        <v>2724</v>
+        <v>61</v>
       </c>
       <c r="D1342" s="2"/>
     </row>
@@ -27720,7 +27717,7 @@
         <v>2997</v>
       </c>
       <c r="C1479" t="s" s="2">
-        <v>2830</v>
+        <v>2998</v>
       </c>
       <c r="D1479" s="2"/>
     </row>
@@ -27729,10 +27726,10 @@
         <v>55</v>
       </c>
       <c r="B1480" t="s" s="2">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="C1480" t="s" s="2">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="D1480" s="2"/>
     </row>
@@ -27741,10 +27738,10 @@
         <v>55</v>
       </c>
       <c r="B1481" t="s" s="2">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="C1481" t="s" s="2">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="D1481" s="2"/>
     </row>
@@ -27753,10 +27750,10 @@
         <v>55</v>
       </c>
       <c r="B1482" t="s" s="2">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C1482" t="s" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="D1482" s="2"/>
     </row>
@@ -27765,10 +27762,10 @@
         <v>55</v>
       </c>
       <c r="B1483" t="s" s="2">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="C1483" t="s" s="2">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="D1483" s="2"/>
     </row>
@@ -27777,10 +27774,10 @@
         <v>55</v>
       </c>
       <c r="B1484" t="s" s="2">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1484" t="s" s="2">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="D1484" s="2"/>
     </row>
@@ -27789,10 +27786,10 @@
         <v>55</v>
       </c>
       <c r="B1485" t="s" s="2">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="C1485" t="s" s="2">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="D1485" s="2"/>
     </row>
@@ -27801,10 +27798,10 @@
         <v>55</v>
       </c>
       <c r="B1486" t="s" s="2">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="C1486" t="s" s="2">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="D1486" s="2"/>
     </row>
@@ -27813,10 +27810,10 @@
         <v>55</v>
       </c>
       <c r="B1487" t="s" s="2">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="C1487" t="s" s="2">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="D1487" s="2"/>
     </row>
@@ -27825,10 +27822,10 @@
         <v>55</v>
       </c>
       <c r="B1488" t="s" s="2">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="C1488" t="s" s="2">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="D1488" s="2"/>
     </row>
@@ -27837,10 +27834,10 @@
         <v>55</v>
       </c>
       <c r="B1489" t="s" s="2">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="C1489" t="s" s="2">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="D1489" s="2"/>
     </row>
@@ -27849,10 +27846,10 @@
         <v>55</v>
       </c>
       <c r="B1490" t="s" s="2">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="C1490" t="s" s="2">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="D1490" s="2"/>
     </row>
@@ -27861,10 +27858,10 @@
         <v>55</v>
       </c>
       <c r="B1491" t="s" s="2">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="C1491" t="s" s="2">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="D1491" s="2"/>
     </row>
@@ -27873,10 +27870,10 @@
         <v>55</v>
       </c>
       <c r="B1492" t="s" s="2">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="C1492" t="s" s="2">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="D1492" s="2"/>
     </row>
@@ -27885,10 +27882,10 @@
         <v>55</v>
       </c>
       <c r="B1493" t="s" s="2">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="C1493" t="s" s="2">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="D1493" s="2"/>
     </row>
@@ -27897,10 +27894,10 @@
         <v>55</v>
       </c>
       <c r="B1494" t="s" s="2">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="C1494" t="s" s="2">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="D1494" s="2"/>
     </row>
@@ -27909,10 +27906,10 @@
         <v>55</v>
       </c>
       <c r="B1495" t="s" s="2">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="C1495" t="s" s="2">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="D1495" s="2"/>
     </row>
@@ -27921,10 +27918,10 @@
         <v>55</v>
       </c>
       <c r="B1496" t="s" s="2">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="C1496" t="s" s="2">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="D1496" s="2"/>
     </row>
@@ -27933,10 +27930,10 @@
         <v>55</v>
       </c>
       <c r="B1497" t="s" s="2">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="C1497" t="s" s="2">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="D1497" s="2"/>
     </row>
@@ -27945,10 +27942,10 @@
         <v>55</v>
       </c>
       <c r="B1498" t="s" s="2">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="C1498" t="s" s="2">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="D1498" s="2"/>
     </row>
@@ -27957,10 +27954,10 @@
         <v>55</v>
       </c>
       <c r="B1499" t="s" s="2">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="C1499" t="s" s="2">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="D1499" s="2"/>
     </row>
@@ -27969,10 +27966,10 @@
         <v>55</v>
       </c>
       <c r="B1500" t="s" s="2">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="C1500" t="s" s="2">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="D1500" s="2"/>
     </row>
@@ -27981,10 +27978,10 @@
         <v>55</v>
       </c>
       <c r="B1501" t="s" s="2">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="C1501" t="s" s="2">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="D1501" s="2"/>
     </row>
@@ -27993,10 +27990,10 @@
         <v>55</v>
       </c>
       <c r="B1502" t="s" s="2">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="C1502" t="s" s="2">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="D1502" s="2"/>
     </row>
@@ -28005,10 +28002,10 @@
         <v>55</v>
       </c>
       <c r="B1503" t="s" s="2">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="C1503" t="s" s="2">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="D1503" s="2"/>
     </row>
@@ -28017,10 +28014,10 @@
         <v>55</v>
       </c>
       <c r="B1504" t="s" s="2">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="C1504" t="s" s="2">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="D1504" s="2"/>
     </row>
@@ -28029,10 +28026,10 @@
         <v>55</v>
       </c>
       <c r="B1505" t="s" s="2">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="C1505" t="s" s="2">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="D1505" s="2"/>
     </row>
@@ -28041,10 +28038,10 @@
         <v>55</v>
       </c>
       <c r="B1506" t="s" s="2">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C1506" t="s" s="2">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="D1506" s="2"/>
     </row>
@@ -28053,10 +28050,10 @@
         <v>55</v>
       </c>
       <c r="B1507" t="s" s="2">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="C1507" t="s" s="2">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="D1507" s="2"/>
     </row>
@@ -28065,10 +28062,10 @@
         <v>55</v>
       </c>
       <c r="B1508" t="s" s="2">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C1508" t="s" s="2">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="D1508" s="2"/>
     </row>
@@ -28077,10 +28074,10 @@
         <v>55</v>
       </c>
       <c r="B1509" t="s" s="2">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C1509" t="s" s="2">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="D1509" s="2"/>
     </row>
@@ -28089,10 +28086,10 @@
         <v>55</v>
       </c>
       <c r="B1510" t="s" s="2">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C1510" t="s" s="2">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="D1510" s="2"/>
     </row>
@@ -28101,10 +28098,10 @@
         <v>55</v>
       </c>
       <c r="B1511" t="s" s="2">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C1511" t="s" s="2">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="D1511" s="2"/>
     </row>
@@ -28113,10 +28110,10 @@
         <v>55</v>
       </c>
       <c r="B1512" t="s" s="2">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C1512" t="s" s="2">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="D1512" s="2"/>
     </row>
@@ -28125,10 +28122,10 @@
         <v>55</v>
       </c>
       <c r="B1513" t="s" s="2">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C1513" t="s" s="2">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="D1513" s="2"/>
     </row>
@@ -28137,10 +28134,10 @@
         <v>55</v>
       </c>
       <c r="B1514" t="s" s="2">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C1514" t="s" s="2">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="D1514" s="2"/>
     </row>
@@ -28149,10 +28146,10 @@
         <v>55</v>
       </c>
       <c r="B1515" t="s" s="2">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C1515" t="s" s="2">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="D1515" s="2"/>
     </row>
@@ -28161,10 +28158,10 @@
         <v>55</v>
       </c>
       <c r="B1516" t="s" s="2">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C1516" t="s" s="2">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="D1516" s="2"/>
     </row>
@@ -28173,10 +28170,10 @@
         <v>55</v>
       </c>
       <c r="B1517" t="s" s="2">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C1517" t="s" s="2">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="D1517" s="2"/>
     </row>
@@ -28185,10 +28182,10 @@
         <v>55</v>
       </c>
       <c r="B1518" t="s" s="2">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C1518" t="s" s="2">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="D1518" s="2"/>
     </row>
@@ -28197,10 +28194,10 @@
         <v>55</v>
       </c>
       <c r="B1519" t="s" s="2">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="C1519" t="s" s="2">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="D1519" s="2"/>
     </row>
@@ -28209,10 +28206,10 @@
         <v>55</v>
       </c>
       <c r="B1520" t="s" s="2">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="C1520" t="s" s="2">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="D1520" s="2"/>
     </row>
@@ -28221,10 +28218,10 @@
         <v>55</v>
       </c>
       <c r="B1521" t="s" s="2">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="C1521" t="s" s="2">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="D1521" s="2"/>
     </row>
@@ -28233,10 +28230,10 @@
         <v>55</v>
       </c>
       <c r="B1522" t="s" s="2">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="C1522" t="s" s="2">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="D1522" s="2"/>
     </row>
@@ -28245,10 +28242,10 @@
         <v>55</v>
       </c>
       <c r="B1523" t="s" s="2">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="C1523" t="s" s="2">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="D1523" s="2"/>
     </row>
@@ -28257,10 +28254,10 @@
         <v>55</v>
       </c>
       <c r="B1524" t="s" s="2">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="C1524" t="s" s="2">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="D1524" s="2"/>
     </row>
@@ -28269,10 +28266,10 @@
         <v>55</v>
       </c>
       <c r="B1525" t="s" s="2">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1525" t="s" s="2">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="D1525" s="2"/>
     </row>
@@ -28281,10 +28278,10 @@
         <v>55</v>
       </c>
       <c r="B1526" t="s" s="2">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="C1526" t="s" s="2">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="D1526" s="2"/>
     </row>
@@ -28293,10 +28290,10 @@
         <v>55</v>
       </c>
       <c r="B1527" t="s" s="2">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="C1527" t="s" s="2">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="D1527" s="2"/>
     </row>
@@ -28305,10 +28302,10 @@
         <v>55</v>
       </c>
       <c r="B1528" t="s" s="2">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="C1528" t="s" s="2">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="D1528" s="2"/>
     </row>
@@ -28317,10 +28314,10 @@
         <v>55</v>
       </c>
       <c r="B1529" t="s" s="2">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="C1529" t="s" s="2">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="D1529" s="2"/>
     </row>
@@ -28329,10 +28326,10 @@
         <v>55</v>
       </c>
       <c r="B1530" t="s" s="2">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="C1530" t="s" s="2">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="D1530" s="2"/>
     </row>
@@ -28341,10 +28338,10 @@
         <v>55</v>
       </c>
       <c r="B1531" t="s" s="2">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C1531" t="s" s="2">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="D1531" s="2"/>
     </row>
@@ -28353,10 +28350,10 @@
         <v>55</v>
       </c>
       <c r="B1532" t="s" s="2">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="C1532" t="s" s="2">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="D1532" s="2"/>
     </row>
@@ -28365,10 +28362,10 @@
         <v>55</v>
       </c>
       <c r="B1533" t="s" s="2">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="C1533" t="s" s="2">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="D1533" s="2"/>
     </row>
@@ -28377,10 +28374,10 @@
         <v>55</v>
       </c>
       <c r="B1534" t="s" s="2">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="C1534" t="s" s="2">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="D1534" s="2"/>
     </row>
@@ -28389,10 +28386,10 @@
         <v>55</v>
       </c>
       <c r="B1535" t="s" s="2">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="C1535" t="s" s="2">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="D1535" s="2"/>
     </row>
@@ -28401,10 +28398,10 @@
         <v>55</v>
       </c>
       <c r="B1536" t="s" s="2">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="C1536" t="s" s="2">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="D1536" s="2"/>
     </row>
@@ -28413,10 +28410,10 @@
         <v>55</v>
       </c>
       <c r="B1537" t="s" s="2">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="C1537" t="s" s="2">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="D1537" s="2"/>
     </row>
@@ -28425,10 +28422,10 @@
         <v>55</v>
       </c>
       <c r="B1538" t="s" s="2">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="C1538" t="s" s="2">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="D1538" s="2"/>
     </row>
@@ -28437,10 +28434,10 @@
         <v>55</v>
       </c>
       <c r="B1539" t="s" s="2">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="C1539" t="s" s="2">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="D1539" s="2"/>
     </row>
@@ -28449,10 +28446,10 @@
         <v>55</v>
       </c>
       <c r="B1540" t="s" s="2">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="C1540" t="s" s="2">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="D1540" s="2"/>
     </row>
@@ -28461,10 +28458,10 @@
         <v>55</v>
       </c>
       <c r="B1541" t="s" s="2">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="C1541" t="s" s="2">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="D1541" s="2"/>
     </row>
@@ -28473,10 +28470,10 @@
         <v>55</v>
       </c>
       <c r="B1542" t="s" s="2">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="C1542" t="s" s="2">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="D1542" s="2"/>
     </row>
@@ -28485,10 +28482,10 @@
         <v>55</v>
       </c>
       <c r="B1543" t="s" s="2">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="C1543" t="s" s="2">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="D1543" s="2"/>
     </row>
@@ -28497,10 +28494,10 @@
         <v>55</v>
       </c>
       <c r="B1544" t="s" s="2">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="C1544" t="s" s="2">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="D1544" s="2"/>
     </row>
@@ -28509,10 +28506,10 @@
         <v>55</v>
       </c>
       <c r="B1545" t="s" s="2">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="C1545" t="s" s="2">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="D1545" s="2"/>
     </row>
@@ -28521,10 +28518,10 @@
         <v>55</v>
       </c>
       <c r="B1546" t="s" s="2">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="C1546" t="s" s="2">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="D1546" s="2"/>
     </row>
@@ -28533,10 +28530,10 @@
         <v>55</v>
       </c>
       <c r="B1547" t="s" s="2">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="C1547" t="s" s="2">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="D1547" s="2"/>
     </row>
@@ -28545,10 +28542,10 @@
         <v>55</v>
       </c>
       <c r="B1548" t="s" s="2">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="C1548" t="s" s="2">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="D1548" s="2"/>
     </row>
@@ -28557,10 +28554,10 @@
         <v>55</v>
       </c>
       <c r="B1549" t="s" s="2">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="C1549" t="s" s="2">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="D1549" s="2"/>
     </row>
@@ -28569,10 +28566,10 @@
         <v>55</v>
       </c>
       <c r="B1550" t="s" s="2">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="C1550" t="s" s="2">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="D1550" s="2"/>
     </row>
@@ -28581,10 +28578,10 @@
         <v>55</v>
       </c>
       <c r="B1551" t="s" s="2">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="C1551" t="s" s="2">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="D1551" s="2"/>
     </row>
@@ -28593,10 +28590,10 @@
         <v>55</v>
       </c>
       <c r="B1552" t="s" s="2">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="C1552" t="s" s="2">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="D1552" s="2"/>
     </row>
@@ -28605,10 +28602,10 @@
         <v>55</v>
       </c>
       <c r="B1553" t="s" s="2">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="C1553" t="s" s="2">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="D1553" s="2"/>
     </row>
@@ -28617,10 +28614,10 @@
         <v>55</v>
       </c>
       <c r="B1554" t="s" s="2">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="C1554" t="s" s="2">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="D1554" s="2"/>
     </row>
@@ -28629,10 +28626,10 @@
         <v>55</v>
       </c>
       <c r="B1555" t="s" s="2">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="C1555" t="s" s="2">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="D1555" s="2"/>
     </row>
@@ -28641,10 +28638,10 @@
         <v>55</v>
       </c>
       <c r="B1556" t="s" s="2">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="C1556" t="s" s="2">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="D1556" s="2"/>
     </row>
@@ -28653,10 +28650,10 @@
         <v>55</v>
       </c>
       <c r="B1557" t="s" s="2">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="C1557" t="s" s="2">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="D1557" s="2"/>
     </row>
@@ -28665,10 +28662,10 @@
         <v>55</v>
       </c>
       <c r="B1558" t="s" s="2">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="C1558" t="s" s="2">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="D1558" s="2"/>
     </row>
@@ -28677,10 +28674,10 @@
         <v>55</v>
       </c>
       <c r="B1559" t="s" s="2">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="C1559" t="s" s="2">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="D1559" s="2"/>
     </row>
@@ -28689,10 +28686,10 @@
         <v>55</v>
       </c>
       <c r="B1560" t="s" s="2">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="C1560" t="s" s="2">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="D1560" s="2"/>
     </row>
@@ -28701,10 +28698,10 @@
         <v>55</v>
       </c>
       <c r="B1561" t="s" s="2">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="C1561" t="s" s="2">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="D1561" s="2"/>
     </row>
@@ -28713,10 +28710,10 @@
         <v>55</v>
       </c>
       <c r="B1562" t="s" s="2">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="C1562" t="s" s="2">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="D1562" s="2"/>
     </row>
@@ -28725,10 +28722,10 @@
         <v>55</v>
       </c>
       <c r="B1563" t="s" s="2">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="C1563" t="s" s="2">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="D1563" s="2"/>
     </row>
@@ -28737,10 +28734,10 @@
         <v>55</v>
       </c>
       <c r="B1564" t="s" s="2">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="C1564" t="s" s="2">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="D1564" s="2"/>
     </row>
@@ -28749,10 +28746,10 @@
         <v>55</v>
       </c>
       <c r="B1565" t="s" s="2">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="C1565" t="s" s="2">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="D1565" s="2"/>
     </row>
@@ -28761,10 +28758,10 @@
         <v>55</v>
       </c>
       <c r="B1566" t="s" s="2">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="C1566" t="s" s="2">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="D1566" s="2"/>
     </row>
@@ -28773,10 +28770,10 @@
         <v>55</v>
       </c>
       <c r="B1567" t="s" s="2">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="C1567" t="s" s="2">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="D1567" s="2"/>
     </row>
@@ -28785,10 +28782,10 @@
         <v>55</v>
       </c>
       <c r="B1568" t="s" s="2">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="C1568" t="s" s="2">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="D1568" s="2"/>
     </row>
@@ -28797,10 +28794,10 @@
         <v>55</v>
       </c>
       <c r="B1569" t="s" s="2">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="C1569" t="s" s="2">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="D1569" s="2"/>
     </row>
@@ -28809,10 +28806,10 @@
         <v>55</v>
       </c>
       <c r="B1570" t="s" s="2">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="C1570" t="s" s="2">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="D1570" s="2"/>
     </row>
@@ -28821,10 +28818,10 @@
         <v>55</v>
       </c>
       <c r="B1571" t="s" s="2">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="C1571" t="s" s="2">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="D1571" s="2"/>
     </row>
@@ -28833,10 +28830,10 @@
         <v>55</v>
       </c>
       <c r="B1572" t="s" s="2">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="C1572" t="s" s="2">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="D1572" s="2"/>
     </row>
@@ -28845,24 +28842,12 @@
         <v>55</v>
       </c>
       <c r="B1573" t="s" s="2">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="C1573" t="s" s="2">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="D1573" s="2"/>
-    </row>
-    <row r="1574">
-      <c r="A1574" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B1574" t="s" s="2">
-        <v>3186</v>
-      </c>
-      <c r="C1574" t="s" s="2">
-        <v>3187</v>
-      </c>
-      <c r="D1574" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="3187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4805" uniqueCount="3205">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202512170000</t>
+    <t>202602240000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:37:59-00:00</t>
+    <t>2026-02-24T15:40:47-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -757,6 +757,12 @@
     <t>Autre complication</t>
   </si>
   <si>
+    <t>GEN-092.01.27</t>
+  </si>
+  <si>
+    <t>Autre facteur de risque</t>
+  </si>
+  <si>
     <t>GEN-092.02.01</t>
   </si>
   <si>
@@ -1045,6 +1051,12 @@
     <t>Autre ressource</t>
   </si>
   <si>
+    <t>GEN-092.06.11</t>
+  </si>
+  <si>
+    <t>Autre collectivité</t>
+  </si>
+  <si>
     <t>GEN-092.07.01</t>
   </si>
   <si>
@@ -2092,12 +2104,6 @@
     <t>Le patient a signé son consentement à la transmission des données au registre ERN cond-GUARD-HEART</t>
   </si>
   <si>
-    <t>GEN-335</t>
-  </si>
-  <si>
-    <t>Le patient a signé son consentement à la transmission des données au registre ERN Heart-Core</t>
-  </si>
-  <si>
     <t>GEN-336</t>
   </si>
   <si>
@@ -2575,6 +2581,42 @@
     <t>Prescriptions</t>
   </si>
   <si>
+    <t>GEN-416</t>
+  </si>
+  <si>
+    <t>Le patient a signé un consentement à la transmission de ses données au registre EuRREB</t>
+  </si>
+  <si>
+    <t>GEN-417</t>
+  </si>
+  <si>
+    <t>Pacsé(e)</t>
+  </si>
+  <si>
+    <t>GEN-418</t>
+  </si>
+  <si>
+    <t>Union libre/Concubinage</t>
+  </si>
+  <si>
+    <t>GEN-419</t>
+  </si>
+  <si>
+    <t>Contact avec un cas de rougeole</t>
+  </si>
+  <si>
+    <t>GEN-420</t>
+  </si>
+  <si>
+    <t>Existence d'autres cas dans l'entourage</t>
+  </si>
+  <si>
+    <t>GEN-421</t>
+  </si>
+  <si>
+    <t>Fréquentation d'une collectivité accueillant des sujets à risque de rougeole grave</t>
+  </si>
+  <si>
     <t>MED-001</t>
   </si>
   <si>
@@ -3031,12 +3073,6 @@
     <t>Décision de prise en soins palliatifs</t>
   </si>
   <si>
-    <t>MED-107</t>
-  </si>
-  <si>
-    <t>Implant</t>
-  </si>
-  <si>
     <t>MED-110</t>
   </si>
   <si>
@@ -4075,13 +4111,13 @@
     <t>MED-363</t>
   </si>
   <si>
-    <t>Hémorragie sévère (manifeste ou récente) ; maladie connue favorisant les hémorragies ; rétinopathie hémorragique (diabétique par ex)</t>
+    <t>Hémorragie sévère (manifeste ou récente), maladie connue favorisant les hémorragies, rétinopathie hémorragique (diabétique par ex)</t>
   </si>
   <si>
     <t>MED-364</t>
   </si>
   <si>
-    <t>Hépatopathie sévère ; pancréatite aiguë</t>
+    <t>Hépatopathie sévère, pancréatite aiguë</t>
   </si>
   <si>
     <t>MED-365</t>
@@ -8387,6 +8423,24 @@
   </si>
   <si>
     <t>Médicament diminuant l’INR</t>
+  </si>
+  <si>
+    <t>MED-1337</t>
+  </si>
+  <si>
+    <t>Le patient (ou le tiers) est-il informé du diagnostic ?</t>
+  </si>
+  <si>
+    <t>MED-1338</t>
+  </si>
+  <si>
+    <t>L'état clinique du patient lui permet-il de répondre à l'investigation ?</t>
+  </si>
+  <si>
+    <t>MED-1339</t>
+  </si>
+  <si>
+    <t>Complication</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -9968,7 +10022,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1573"/>
+  <dimension ref="A1:D1582"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -12429,7 +12483,7 @@
         <v>461</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>35</v>
+        <v>462</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -12438,10 +12492,10 @@
         <v>55</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -12450,10 +12504,10 @@
         <v>55</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>465</v>
+        <v>35</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -14253,7 +14307,7 @@
         <v>764</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>91</v>
+        <v>765</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -14262,10 +14316,10 @@
         <v>55</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>766</v>
+        <v>91</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -16413,7 +16467,7 @@
         <v>1123</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>198</v>
+        <v>1124</v>
       </c>
       <c r="D537" s="2"/>
     </row>
@@ -16422,10 +16476,10 @@
         <v>55</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D538" s="2"/>
     </row>
@@ -16434,10 +16488,10 @@
         <v>55</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D539" s="2"/>
     </row>
@@ -16446,10 +16500,10 @@
         <v>55</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D540" s="2"/>
     </row>
@@ -16458,10 +16512,10 @@
         <v>55</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D541" s="2"/>
     </row>
@@ -16470,10 +16524,10 @@
         <v>55</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D542" s="2"/>
     </row>
@@ -16482,10 +16536,10 @@
         <v>55</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1135</v>
+        <v>198</v>
       </c>
       <c r="D543" s="2"/>
     </row>
@@ -21045,7 +21099,7 @@
         <v>1894</v>
       </c>
       <c r="C923" t="s" s="2">
-        <v>563</v>
+        <v>1895</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -21054,10 +21108,10 @@
         <v>55</v>
       </c>
       <c r="B924" t="s" s="2">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C924" t="s" s="2">
-        <v>565</v>
+        <v>1897</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -21066,10 +21120,10 @@
         <v>55</v>
       </c>
       <c r="B925" t="s" s="2">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C925" t="s" s="2">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="D925" s="2"/>
     </row>
@@ -21078,10 +21132,10 @@
         <v>55</v>
       </c>
       <c r="B926" t="s" s="2">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C926" t="s" s="2">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="D926" s="2"/>
     </row>
@@ -21090,10 +21144,10 @@
         <v>55</v>
       </c>
       <c r="B927" t="s" s="2">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C927" t="s" s="2">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="D927" s="2"/>
     </row>
@@ -21102,10 +21156,10 @@
         <v>55</v>
       </c>
       <c r="B928" t="s" s="2">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C928" t="s" s="2">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="D928" s="2"/>
     </row>
@@ -21114,10 +21168,10 @@
         <v>55</v>
       </c>
       <c r="B929" t="s" s="2">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C929" t="s" s="2">
-        <v>1905</v>
+        <v>567</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -21126,10 +21180,10 @@
         <v>55</v>
       </c>
       <c r="B930" t="s" s="2">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="C930" t="s" s="2">
-        <v>1907</v>
+        <v>569</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -21585,7 +21639,7 @@
         <v>1982</v>
       </c>
       <c r="C968" t="s" s="2">
-        <v>1937</v>
+        <v>1983</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -21594,10 +21648,10 @@
         <v>55</v>
       </c>
       <c r="B969" t="s" s="2">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C969" t="s" s="2">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D969" s="2"/>
     </row>
@@ -21606,10 +21660,10 @@
         <v>55</v>
       </c>
       <c r="B970" t="s" s="2">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C970" t="s" s="2">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D970" s="2"/>
     </row>
@@ -21618,10 +21672,10 @@
         <v>55</v>
       </c>
       <c r="B971" t="s" s="2">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C971" t="s" s="2">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="D971" s="2"/>
     </row>
@@ -21630,10 +21684,10 @@
         <v>55</v>
       </c>
       <c r="B972" t="s" s="2">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C972" t="s" s="2">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D972" s="2"/>
     </row>
@@ -21642,10 +21696,10 @@
         <v>55</v>
       </c>
       <c r="B973" t="s" s="2">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C973" t="s" s="2">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D973" s="2"/>
     </row>
@@ -21654,10 +21708,10 @@
         <v>55</v>
       </c>
       <c r="B974" t="s" s="2">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C974" t="s" s="2">
-        <v>1994</v>
+        <v>1949</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -23157,7 +23211,7 @@
         <v>2243</v>
       </c>
       <c r="C1099" t="s" s="2">
-        <v>2192</v>
+        <v>2244</v>
       </c>
       <c r="D1099" s="2"/>
     </row>
@@ -23166,10 +23220,10 @@
         <v>55</v>
       </c>
       <c r="B1100" t="s" s="2">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C1100" t="s" s="2">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="D1100" s="2"/>
     </row>
@@ -23178,10 +23232,10 @@
         <v>55</v>
       </c>
       <c r="B1101" t="s" s="2">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="C1101" t="s" s="2">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="D1101" s="2"/>
     </row>
@@ -23190,10 +23244,10 @@
         <v>55</v>
       </c>
       <c r="B1102" t="s" s="2">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="C1102" t="s" s="2">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="D1102" s="2"/>
     </row>
@@ -23202,10 +23256,10 @@
         <v>55</v>
       </c>
       <c r="B1103" t="s" s="2">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C1103" t="s" s="2">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="D1103" s="2"/>
     </row>
@@ -23214,10 +23268,10 @@
         <v>55</v>
       </c>
       <c r="B1104" t="s" s="2">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="C1104" t="s" s="2">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="D1104" s="2"/>
     </row>
@@ -23226,10 +23280,10 @@
         <v>55</v>
       </c>
       <c r="B1105" t="s" s="2">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="C1105" t="s" s="2">
-        <v>2255</v>
+        <v>2204</v>
       </c>
       <c r="D1105" s="2"/>
     </row>
@@ -25437,7 +25491,7 @@
         <v>2622</v>
       </c>
       <c r="C1289" t="s" s="2">
-        <v>2575</v>
+        <v>2623</v>
       </c>
       <c r="D1289" s="2"/>
     </row>
@@ -25446,10 +25500,10 @@
         <v>55</v>
       </c>
       <c r="B1290" t="s" s="2">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="C1290" t="s" s="2">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="D1290" s="2"/>
     </row>
@@ -25458,10 +25512,10 @@
         <v>55</v>
       </c>
       <c r="B1291" t="s" s="2">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="C1291" t="s" s="2">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="D1291" s="2"/>
     </row>
@@ -25470,10 +25524,10 @@
         <v>55</v>
       </c>
       <c r="B1292" t="s" s="2">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="C1292" t="s" s="2">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="D1292" s="2"/>
     </row>
@@ -25482,10 +25536,10 @@
         <v>55</v>
       </c>
       <c r="B1293" t="s" s="2">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="C1293" t="s" s="2">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="D1293" s="2"/>
     </row>
@@ -25494,10 +25548,10 @@
         <v>55</v>
       </c>
       <c r="B1294" t="s" s="2">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="C1294" t="s" s="2">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="D1294" s="2"/>
     </row>
@@ -25506,10 +25560,10 @@
         <v>55</v>
       </c>
       <c r="B1295" t="s" s="2">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="C1295" t="s" s="2">
-        <v>2634</v>
+        <v>2587</v>
       </c>
       <c r="D1295" s="2"/>
     </row>
@@ -25893,7 +25947,7 @@
         <v>2697</v>
       </c>
       <c r="C1327" t="s" s="2">
-        <v>296</v>
+        <v>2698</v>
       </c>
       <c r="D1327" s="2"/>
     </row>
@@ -25902,10 +25956,10 @@
         <v>55</v>
       </c>
       <c r="B1328" t="s" s="2">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="C1328" t="s" s="2">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="D1328" s="2"/>
     </row>
@@ -25914,10 +25968,10 @@
         <v>55</v>
       </c>
       <c r="B1329" t="s" s="2">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="C1329" t="s" s="2">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="D1329" s="2"/>
     </row>
@@ -25926,10 +25980,10 @@
         <v>55</v>
       </c>
       <c r="B1330" t="s" s="2">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="C1330" t="s" s="2">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="D1330" s="2"/>
     </row>
@@ -25938,10 +25992,10 @@
         <v>55</v>
       </c>
       <c r="B1331" t="s" s="2">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="C1331" t="s" s="2">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="D1331" s="2"/>
     </row>
@@ -25950,10 +26004,10 @@
         <v>55</v>
       </c>
       <c r="B1332" t="s" s="2">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="C1332" t="s" s="2">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="D1332" s="2"/>
     </row>
@@ -25962,10 +26016,10 @@
         <v>55</v>
       </c>
       <c r="B1333" t="s" s="2">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="C1333" t="s" s="2">
-        <v>2709</v>
+        <v>298</v>
       </c>
       <c r="D1333" s="2"/>
     </row>
@@ -26049,7 +26103,7 @@
         <v>2722</v>
       </c>
       <c r="C1340" t="s" s="2">
-        <v>57</v>
+        <v>2723</v>
       </c>
       <c r="D1340" s="2"/>
     </row>
@@ -26058,10 +26112,10 @@
         <v>55</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="C1341" t="s" s="2">
-        <v>59</v>
+        <v>2725</v>
       </c>
       <c r="D1341" s="2"/>
     </row>
@@ -26070,10 +26124,10 @@
         <v>55</v>
       </c>
       <c r="B1342" t="s" s="2">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="C1342" t="s" s="2">
-        <v>61</v>
+        <v>2727</v>
       </c>
       <c r="D1342" s="2"/>
     </row>
@@ -26082,10 +26136,10 @@
         <v>55</v>
       </c>
       <c r="B1343" t="s" s="2">
-        <v>2725</v>
+        <v>2728</v>
       </c>
       <c r="C1343" t="s" s="2">
-        <v>2726</v>
+        <v>2729</v>
       </c>
       <c r="D1343" s="2"/>
     </row>
@@ -26094,10 +26148,10 @@
         <v>55</v>
       </c>
       <c r="B1344" t="s" s="2">
-        <v>2727</v>
+        <v>2730</v>
       </c>
       <c r="C1344" t="s" s="2">
-        <v>2728</v>
+        <v>2731</v>
       </c>
       <c r="D1344" s="2"/>
     </row>
@@ -26106,10 +26160,10 @@
         <v>55</v>
       </c>
       <c r="B1345" t="s" s="2">
-        <v>2729</v>
+        <v>2732</v>
       </c>
       <c r="C1345" t="s" s="2">
-        <v>2730</v>
+        <v>2733</v>
       </c>
       <c r="D1345" s="2"/>
     </row>
@@ -26118,10 +26172,10 @@
         <v>55</v>
       </c>
       <c r="B1346" t="s" s="2">
-        <v>2731</v>
+        <v>2734</v>
       </c>
       <c r="C1346" t="s" s="2">
-        <v>2732</v>
+        <v>57</v>
       </c>
       <c r="D1346" s="2"/>
     </row>
@@ -26130,10 +26184,10 @@
         <v>55</v>
       </c>
       <c r="B1347" t="s" s="2">
-        <v>2733</v>
+        <v>2735</v>
       </c>
       <c r="C1347" t="s" s="2">
-        <v>2734</v>
+        <v>59</v>
       </c>
       <c r="D1347" s="2"/>
     </row>
@@ -26142,10 +26196,10 @@
         <v>55</v>
       </c>
       <c r="B1348" t="s" s="2">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="C1348" t="s" s="2">
-        <v>2736</v>
+        <v>61</v>
       </c>
       <c r="D1348" s="2"/>
     </row>
@@ -28848,6 +28902,114 @@
         <v>3186</v>
       </c>
       <c r="D1573" s="2"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1574" t="s" s="2">
+        <v>3187</v>
+      </c>
+      <c r="C1574" t="s" s="2">
+        <v>3188</v>
+      </c>
+      <c r="D1574" s="2"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1575" t="s" s="2">
+        <v>3189</v>
+      </c>
+      <c r="C1575" t="s" s="2">
+        <v>3190</v>
+      </c>
+      <c r="D1575" s="2"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1576" t="s" s="2">
+        <v>3191</v>
+      </c>
+      <c r="C1576" t="s" s="2">
+        <v>3192</v>
+      </c>
+      <c r="D1576" s="2"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1577" t="s" s="2">
+        <v>3193</v>
+      </c>
+      <c r="C1577" t="s" s="2">
+        <v>3194</v>
+      </c>
+      <c r="D1577" s="2"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1578" t="s" s="2">
+        <v>3195</v>
+      </c>
+      <c r="C1578" t="s" s="2">
+        <v>3196</v>
+      </c>
+      <c r="D1578" s="2"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1579" t="s" s="2">
+        <v>3197</v>
+      </c>
+      <c r="C1579" t="s" s="2">
+        <v>3198</v>
+      </c>
+      <c r="D1579" s="2"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1580" t="s" s="2">
+        <v>3199</v>
+      </c>
+      <c r="C1580" t="s" s="2">
+        <v>3200</v>
+      </c>
+      <c r="D1580" s="2"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1581" t="s" s="2">
+        <v>3201</v>
+      </c>
+      <c r="C1581" t="s" s="2">
+        <v>3202</v>
+      </c>
+      <c r="D1581" s="2"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1582" t="s" s="2">
+        <v>3203</v>
+      </c>
+      <c r="C1582" t="s" s="2">
+        <v>3204</v>
+      </c>
+      <c r="D1582" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4805" uniqueCount="3205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="3253">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202602240000</t>
+    <t>202603110000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T15:40:47-00:00</t>
+    <t>2026-03-11T14:52:01-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2617,6 +2617,60 @@
     <t>Fréquentation d'une collectivité accueillant des sujets à risque de rougeole grave</t>
   </si>
   <si>
+    <t>GEN-422</t>
+  </si>
+  <si>
+    <t>Le patient a signé un consentement à la transmission de ses données au(x) registre(s) de l'ERN GloBE-Reg</t>
+  </si>
+  <si>
+    <t>GEN-423</t>
+  </si>
+  <si>
+    <t>Présence de sujet à risque de rougeole grave dans l’entourage du cas (femme enceinte, immunodéprimé, nourrisson)</t>
+  </si>
+  <si>
+    <t>GEN-424</t>
+  </si>
+  <si>
+    <t>Administration d’immunoglobulines aux contacts à risque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-425</t>
+  </si>
+  <si>
+    <t>Nombre d'admministration d'immunoglobines aux contacts àrisque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-426</t>
+  </si>
+  <si>
+    <t>Administration dans les 72 heures suivant le 1er contact du vaccin ROR aux personnes contact</t>
+  </si>
+  <si>
+    <t>GEN-427</t>
+  </si>
+  <si>
+    <t>Nombre d'administration dans les 72 heures suivant le 1er contact du vaccin ROR aux personnes contact</t>
+  </si>
+  <si>
+    <t>GEN-428</t>
+  </si>
+  <si>
+    <t>Souhaitez-vous recevoir des kits pour prélèvements et envois d’échantillons de salive au CNR (recherche d’IgM/PCR) ?</t>
+  </si>
+  <si>
+    <t>GEN-429</t>
+  </si>
+  <si>
+    <t>Nombre de kits</t>
+  </si>
+  <si>
+    <t>GEN-430</t>
+  </si>
+  <si>
+    <t>Séjour à l’étranger pour les autres cas de rougeole dans l'entourage</t>
+  </si>
+  <si>
     <t>MED-001</t>
   </si>
   <si>
@@ -8443,6 +8497,66 @@
     <t>Complication</t>
   </si>
   <si>
+    <t>MED-1340</t>
+  </si>
+  <si>
+    <t>Vaccination autre flavivirus</t>
+  </si>
+  <si>
+    <t>MED-1341</t>
+  </si>
+  <si>
+    <t>Autre(s) exposition(s)</t>
+  </si>
+  <si>
+    <t>MED-1342</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 60-65 ans</t>
+  </si>
+  <si>
+    <t>MED-1343</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 66-69 ans</t>
+  </si>
+  <si>
+    <t>MED-1344</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1345</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 76 ans et plus</t>
+  </si>
+  <si>
+    <t>MED-1346</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 18-25 ans</t>
+  </si>
+  <si>
+    <t>MED-1347</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 45-50 ans</t>
+  </si>
+  <si>
+    <t>MED-1348</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 60-65 ans</t>
+  </si>
+  <si>
+    <t>MED-1349</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
     <t>ORG-001</t>
   </si>
   <si>
@@ -9317,6 +9431,36 @@
   </si>
   <si>
     <t>Intervenant à domicile</t>
+  </si>
+  <si>
+    <t>ORG-225</t>
+  </si>
+  <si>
+    <t>RCP Métastase osseuse</t>
+  </si>
+  <si>
+    <t>ORG-226</t>
+  </si>
+  <si>
+    <t>RCP Cancers rares</t>
+  </si>
+  <si>
+    <t>ORG-227</t>
+  </si>
+  <si>
+    <t>Domicile ou milieu ordinaire</t>
+  </si>
+  <si>
+    <t>ORG-228</t>
+  </si>
+  <si>
+    <t>Etablissement médico-social</t>
+  </si>
+  <si>
+    <t>ORG-229</t>
+  </si>
+  <si>
+    <t>Provenance inconnue</t>
   </si>
   <si>
     <t>PAT-001</t>
@@ -10022,7 +10166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1582"/>
+  <dimension ref="A1:D1606"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16539,7 +16683,7 @@
         <v>1135</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>198</v>
+        <v>1136</v>
       </c>
       <c r="D543" s="2"/>
     </row>
@@ -16548,10 +16692,10 @@
         <v>55</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D544" s="2"/>
     </row>
@@ -16560,10 +16704,10 @@
         <v>55</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D545" s="2"/>
     </row>
@@ -16572,10 +16716,10 @@
         <v>55</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -16584,10 +16728,10 @@
         <v>55</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D547" s="2"/>
     </row>
@@ -16596,10 +16740,10 @@
         <v>55</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -16608,10 +16752,10 @@
         <v>55</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -16620,10 +16764,10 @@
         <v>55</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D550" s="2"/>
     </row>
@@ -16632,10 +16776,10 @@
         <v>55</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -16644,10 +16788,10 @@
         <v>55</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1153</v>
+        <v>198</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -21171,7 +21315,7 @@
         <v>1906</v>
       </c>
       <c r="C929" t="s" s="2">
-        <v>567</v>
+        <v>1907</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -21180,10 +21324,10 @@
         <v>55</v>
       </c>
       <c r="B930" t="s" s="2">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="C930" t="s" s="2">
-        <v>569</v>
+        <v>1909</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -21192,10 +21336,10 @@
         <v>55</v>
       </c>
       <c r="B931" t="s" s="2">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="C931" t="s" s="2">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -21204,10 +21348,10 @@
         <v>55</v>
       </c>
       <c r="B932" t="s" s="2">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="C932" t="s" s="2">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -21216,10 +21360,10 @@
         <v>55</v>
       </c>
       <c r="B933" t="s" s="2">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="C933" t="s" s="2">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -21228,10 +21372,10 @@
         <v>55</v>
       </c>
       <c r="B934" t="s" s="2">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="C934" t="s" s="2">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -21240,10 +21384,10 @@
         <v>55</v>
       </c>
       <c r="B935" t="s" s="2">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="C935" t="s" s="2">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -21252,10 +21396,10 @@
         <v>55</v>
       </c>
       <c r="B936" t="s" s="2">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C936" t="s" s="2">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -21264,10 +21408,10 @@
         <v>55</v>
       </c>
       <c r="B937" t="s" s="2">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="C937" t="s" s="2">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -21276,10 +21420,10 @@
         <v>55</v>
       </c>
       <c r="B938" t="s" s="2">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="C938" t="s" s="2">
-        <v>1923</v>
+        <v>567</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -21288,10 +21432,10 @@
         <v>55</v>
       </c>
       <c r="B939" t="s" s="2">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="C939" t="s" s="2">
-        <v>1925</v>
+        <v>569</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -21711,7 +21855,7 @@
         <v>1994</v>
       </c>
       <c r="C974" t="s" s="2">
-        <v>1949</v>
+        <v>1995</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -21720,10 +21864,10 @@
         <v>55</v>
       </c>
       <c r="B975" t="s" s="2">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="C975" t="s" s="2">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -21732,10 +21876,10 @@
         <v>55</v>
       </c>
       <c r="B976" t="s" s="2">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C976" t="s" s="2">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -21744,10 +21888,10 @@
         <v>55</v>
       </c>
       <c r="B977" t="s" s="2">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C977" t="s" s="2">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -21756,10 +21900,10 @@
         <v>55</v>
       </c>
       <c r="B978" t="s" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C978" t="s" s="2">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -21768,10 +21912,10 @@
         <v>55</v>
       </c>
       <c r="B979" t="s" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C979" t="s" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -21780,10 +21924,10 @@
         <v>55</v>
       </c>
       <c r="B980" t="s" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C980" t="s" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -21792,10 +21936,10 @@
         <v>55</v>
       </c>
       <c r="B981" t="s" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C981" t="s" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -21804,10 +21948,10 @@
         <v>55</v>
       </c>
       <c r="B982" t="s" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C982" t="s" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -21816,10 +21960,10 @@
         <v>55</v>
       </c>
       <c r="B983" t="s" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C983" t="s" s="2">
-        <v>2012</v>
+        <v>1967</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -23283,7 +23427,7 @@
         <v>2255</v>
       </c>
       <c r="C1105" t="s" s="2">
-        <v>2204</v>
+        <v>2256</v>
       </c>
       <c r="D1105" s="2"/>
     </row>
@@ -23292,10 +23436,10 @@
         <v>55</v>
       </c>
       <c r="B1106" t="s" s="2">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="C1106" t="s" s="2">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="D1106" s="2"/>
     </row>
@@ -23304,10 +23448,10 @@
         <v>55</v>
       </c>
       <c r="B1107" t="s" s="2">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="C1107" t="s" s="2">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="D1107" s="2"/>
     </row>
@@ -23316,10 +23460,10 @@
         <v>55</v>
       </c>
       <c r="B1108" t="s" s="2">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="C1108" t="s" s="2">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="D1108" s="2"/>
     </row>
@@ -23328,10 +23472,10 @@
         <v>55</v>
       </c>
       <c r="B1109" t="s" s="2">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="C1109" t="s" s="2">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="D1109" s="2"/>
     </row>
@@ -23340,10 +23484,10 @@
         <v>55</v>
       </c>
       <c r="B1110" t="s" s="2">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C1110" t="s" s="2">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="D1110" s="2"/>
     </row>
@@ -23352,10 +23496,10 @@
         <v>55</v>
       </c>
       <c r="B1111" t="s" s="2">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="C1111" t="s" s="2">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="D1111" s="2"/>
     </row>
@@ -23364,10 +23508,10 @@
         <v>55</v>
       </c>
       <c r="B1112" t="s" s="2">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C1112" t="s" s="2">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="D1112" s="2"/>
     </row>
@@ -23376,10 +23520,10 @@
         <v>55</v>
       </c>
       <c r="B1113" t="s" s="2">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C1113" t="s" s="2">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="D1113" s="2"/>
     </row>
@@ -23388,10 +23532,10 @@
         <v>55</v>
       </c>
       <c r="B1114" t="s" s="2">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C1114" t="s" s="2">
-        <v>2273</v>
+        <v>2222</v>
       </c>
       <c r="D1114" s="2"/>
     </row>
@@ -25563,7 +25707,7 @@
         <v>2634</v>
       </c>
       <c r="C1295" t="s" s="2">
-        <v>2587</v>
+        <v>2635</v>
       </c>
       <c r="D1295" s="2"/>
     </row>
@@ -25572,10 +25716,10 @@
         <v>55</v>
       </c>
       <c r="B1296" t="s" s="2">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="C1296" t="s" s="2">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="D1296" s="2"/>
     </row>
@@ -25584,10 +25728,10 @@
         <v>55</v>
       </c>
       <c r="B1297" t="s" s="2">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="C1297" t="s" s="2">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="D1297" s="2"/>
     </row>
@@ -25596,10 +25740,10 @@
         <v>55</v>
       </c>
       <c r="B1298" t="s" s="2">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="C1298" t="s" s="2">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="D1298" s="2"/>
     </row>
@@ -25608,10 +25752,10 @@
         <v>55</v>
       </c>
       <c r="B1299" t="s" s="2">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="C1299" t="s" s="2">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="D1299" s="2"/>
     </row>
@@ -25620,10 +25764,10 @@
         <v>55</v>
       </c>
       <c r="B1300" t="s" s="2">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="C1300" t="s" s="2">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="D1300" s="2"/>
     </row>
@@ -25632,10 +25776,10 @@
         <v>55</v>
       </c>
       <c r="B1301" t="s" s="2">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="C1301" t="s" s="2">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="D1301" s="2"/>
     </row>
@@ -25644,10 +25788,10 @@
         <v>55</v>
       </c>
       <c r="B1302" t="s" s="2">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="C1302" t="s" s="2">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="D1302" s="2"/>
     </row>
@@ -25656,10 +25800,10 @@
         <v>55</v>
       </c>
       <c r="B1303" t="s" s="2">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="C1303" t="s" s="2">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="D1303" s="2"/>
     </row>
@@ -25668,10 +25812,10 @@
         <v>55</v>
       </c>
       <c r="B1304" t="s" s="2">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="C1304" t="s" s="2">
-        <v>2652</v>
+        <v>2605</v>
       </c>
       <c r="D1304" s="2"/>
     </row>
@@ -26019,7 +26163,7 @@
         <v>2709</v>
       </c>
       <c r="C1333" t="s" s="2">
-        <v>298</v>
+        <v>2710</v>
       </c>
       <c r="D1333" s="2"/>
     </row>
@@ -26028,10 +26172,10 @@
         <v>55</v>
       </c>
       <c r="B1334" t="s" s="2">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="C1334" t="s" s="2">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="D1334" s="2"/>
     </row>
@@ -26040,10 +26184,10 @@
         <v>55</v>
       </c>
       <c r="B1335" t="s" s="2">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="C1335" t="s" s="2">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="D1335" s="2"/>
     </row>
@@ -26052,10 +26196,10 @@
         <v>55</v>
       </c>
       <c r="B1336" t="s" s="2">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="C1336" t="s" s="2">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="D1336" s="2"/>
     </row>
@@ -26064,10 +26208,10 @@
         <v>55</v>
       </c>
       <c r="B1337" t="s" s="2">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="C1337" t="s" s="2">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="D1337" s="2"/>
     </row>
@@ -26076,10 +26220,10 @@
         <v>55</v>
       </c>
       <c r="B1338" t="s" s="2">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="C1338" t="s" s="2">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D1338" s="2"/>
     </row>
@@ -26088,10 +26232,10 @@
         <v>55</v>
       </c>
       <c r="B1339" t="s" s="2">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="C1339" t="s" s="2">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="D1339" s="2"/>
     </row>
@@ -26100,10 +26244,10 @@
         <v>55</v>
       </c>
       <c r="B1340" t="s" s="2">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="C1340" t="s" s="2">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="D1340" s="2"/>
     </row>
@@ -26112,10 +26256,10 @@
         <v>55</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="C1341" t="s" s="2">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="D1341" s="2"/>
     </row>
@@ -26124,10 +26268,10 @@
         <v>55</v>
       </c>
       <c r="B1342" t="s" s="2">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="C1342" t="s" s="2">
-        <v>2727</v>
+        <v>298</v>
       </c>
       <c r="D1342" s="2"/>
     </row>
@@ -26175,7 +26319,7 @@
         <v>2734</v>
       </c>
       <c r="C1346" t="s" s="2">
-        <v>57</v>
+        <v>2735</v>
       </c>
       <c r="D1346" s="2"/>
     </row>
@@ -26184,10 +26328,10 @@
         <v>55</v>
       </c>
       <c r="B1347" t="s" s="2">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="C1347" t="s" s="2">
-        <v>59</v>
+        <v>2737</v>
       </c>
       <c r="D1347" s="2"/>
     </row>
@@ -26196,10 +26340,10 @@
         <v>55</v>
       </c>
       <c r="B1348" t="s" s="2">
-        <v>2736</v>
+        <v>2738</v>
       </c>
       <c r="C1348" t="s" s="2">
-        <v>61</v>
+        <v>2739</v>
       </c>
       <c r="D1348" s="2"/>
     </row>
@@ -26208,10 +26352,10 @@
         <v>55</v>
       </c>
       <c r="B1349" t="s" s="2">
-        <v>2737</v>
+        <v>2740</v>
       </c>
       <c r="C1349" t="s" s="2">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="D1349" s="2"/>
     </row>
@@ -26220,10 +26364,10 @@
         <v>55</v>
       </c>
       <c r="B1350" t="s" s="2">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C1350" t="s" s="2">
-        <v>2740</v>
+        <v>2743</v>
       </c>
       <c r="D1350" s="2"/>
     </row>
@@ -26232,10 +26376,10 @@
         <v>55</v>
       </c>
       <c r="B1351" t="s" s="2">
-        <v>2741</v>
+        <v>2744</v>
       </c>
       <c r="C1351" t="s" s="2">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D1351" s="2"/>
     </row>
@@ -26244,10 +26388,10 @@
         <v>55</v>
       </c>
       <c r="B1352" t="s" s="2">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="C1352" t="s" s="2">
-        <v>2744</v>
+        <v>2747</v>
       </c>
       <c r="D1352" s="2"/>
     </row>
@@ -26256,10 +26400,10 @@
         <v>55</v>
       </c>
       <c r="B1353" t="s" s="2">
-        <v>2745</v>
+        <v>2748</v>
       </c>
       <c r="C1353" t="s" s="2">
-        <v>2746</v>
+        <v>2749</v>
       </c>
       <c r="D1353" s="2"/>
     </row>
@@ -26268,10 +26412,10 @@
         <v>55</v>
       </c>
       <c r="B1354" t="s" s="2">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="C1354" t="s" s="2">
-        <v>2748</v>
+        <v>2751</v>
       </c>
       <c r="D1354" s="2"/>
     </row>
@@ -26280,10 +26424,10 @@
         <v>55</v>
       </c>
       <c r="B1355" t="s" s="2">
-        <v>2749</v>
+        <v>2752</v>
       </c>
       <c r="C1355" t="s" s="2">
-        <v>2750</v>
+        <v>57</v>
       </c>
       <c r="D1355" s="2"/>
     </row>
@@ -26292,10 +26436,10 @@
         <v>55</v>
       </c>
       <c r="B1356" t="s" s="2">
-        <v>2751</v>
+        <v>2753</v>
       </c>
       <c r="C1356" t="s" s="2">
-        <v>2752</v>
+        <v>59</v>
       </c>
       <c r="D1356" s="2"/>
     </row>
@@ -26304,10 +26448,10 @@
         <v>55</v>
       </c>
       <c r="B1357" t="s" s="2">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="C1357" t="s" s="2">
-        <v>2754</v>
+        <v>61</v>
       </c>
       <c r="D1357" s="2"/>
     </row>
@@ -29010,6 +29154,294 @@
         <v>3204</v>
       </c>
       <c r="D1582" s="2"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1583" t="s" s="2">
+        <v>3205</v>
+      </c>
+      <c r="C1583" t="s" s="2">
+        <v>3206</v>
+      </c>
+      <c r="D1583" s="2"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1584" t="s" s="2">
+        <v>3207</v>
+      </c>
+      <c r="C1584" t="s" s="2">
+        <v>3208</v>
+      </c>
+      <c r="D1584" s="2"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1585" t="s" s="2">
+        <v>3209</v>
+      </c>
+      <c r="C1585" t="s" s="2">
+        <v>3210</v>
+      </c>
+      <c r="D1585" s="2"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1586" t="s" s="2">
+        <v>3211</v>
+      </c>
+      <c r="C1586" t="s" s="2">
+        <v>3212</v>
+      </c>
+      <c r="D1586" s="2"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1587" t="s" s="2">
+        <v>3213</v>
+      </c>
+      <c r="C1587" t="s" s="2">
+        <v>3214</v>
+      </c>
+      <c r="D1587" s="2"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1588" t="s" s="2">
+        <v>3215</v>
+      </c>
+      <c r="C1588" t="s" s="2">
+        <v>3216</v>
+      </c>
+      <c r="D1588" s="2"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1589" t="s" s="2">
+        <v>3217</v>
+      </c>
+      <c r="C1589" t="s" s="2">
+        <v>3218</v>
+      </c>
+      <c r="D1589" s="2"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1590" t="s" s="2">
+        <v>3219</v>
+      </c>
+      <c r="C1590" t="s" s="2">
+        <v>3220</v>
+      </c>
+      <c r="D1590" s="2"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1591" t="s" s="2">
+        <v>3221</v>
+      </c>
+      <c r="C1591" t="s" s="2">
+        <v>3222</v>
+      </c>
+      <c r="D1591" s="2"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1592" t="s" s="2">
+        <v>3223</v>
+      </c>
+      <c r="C1592" t="s" s="2">
+        <v>3224</v>
+      </c>
+      <c r="D1592" s="2"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1593" t="s" s="2">
+        <v>3225</v>
+      </c>
+      <c r="C1593" t="s" s="2">
+        <v>3226</v>
+      </c>
+      <c r="D1593" s="2"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1594" t="s" s="2">
+        <v>3227</v>
+      </c>
+      <c r="C1594" t="s" s="2">
+        <v>3228</v>
+      </c>
+      <c r="D1594" s="2"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1595" t="s" s="2">
+        <v>3229</v>
+      </c>
+      <c r="C1595" t="s" s="2">
+        <v>3230</v>
+      </c>
+      <c r="D1595" s="2"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1596" t="s" s="2">
+        <v>3231</v>
+      </c>
+      <c r="C1596" t="s" s="2">
+        <v>3232</v>
+      </c>
+      <c r="D1596" s="2"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1597" t="s" s="2">
+        <v>3233</v>
+      </c>
+      <c r="C1597" t="s" s="2">
+        <v>3234</v>
+      </c>
+      <c r="D1597" s="2"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1598" t="s" s="2">
+        <v>3235</v>
+      </c>
+      <c r="C1598" t="s" s="2">
+        <v>3236</v>
+      </c>
+      <c r="D1598" s="2"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1599" t="s" s="2">
+        <v>3237</v>
+      </c>
+      <c r="C1599" t="s" s="2">
+        <v>3238</v>
+      </c>
+      <c r="D1599" s="2"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1600" t="s" s="2">
+        <v>3239</v>
+      </c>
+      <c r="C1600" t="s" s="2">
+        <v>3240</v>
+      </c>
+      <c r="D1600" s="2"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1601" t="s" s="2">
+        <v>3241</v>
+      </c>
+      <c r="C1601" t="s" s="2">
+        <v>3242</v>
+      </c>
+      <c r="D1601" s="2"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1602" t="s" s="2">
+        <v>3243</v>
+      </c>
+      <c r="C1602" t="s" s="2">
+        <v>3244</v>
+      </c>
+      <c r="D1602" s="2"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1603" t="s" s="2">
+        <v>3245</v>
+      </c>
+      <c r="C1603" t="s" s="2">
+        <v>3246</v>
+      </c>
+      <c r="D1603" s="2"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1604" t="s" s="2">
+        <v>3247</v>
+      </c>
+      <c r="C1604" t="s" s="2">
+        <v>3248</v>
+      </c>
+      <c r="D1604" s="2"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1605" t="s" s="2">
+        <v>3249</v>
+      </c>
+      <c r="C1605" t="s" s="2">
+        <v>3250</v>
+      </c>
+      <c r="D1605" s="2"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1606" t="s" s="2">
+        <v>3251</v>
+      </c>
+      <c r="C1606" t="s" s="2">
+        <v>3252</v>
+      </c>
+      <c r="D1606" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="3253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4880" uniqueCount="3255">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202603110000</t>
+    <t>202604200000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:52:01-00:00</t>
+    <t>2026-04-20T11:06:51-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8555,6 +8555,12 @@
   </si>
   <si>
     <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1350</t>
+  </si>
+  <si>
+    <t>Entrées/sorties hydro-électrolytiques</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10166,7 +10172,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1606"/>
+  <dimension ref="A1:D1607"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29443,6 +29449,18 @@
       </c>
       <c r="D1606" s="2"/>
     </row>
+    <row r="1607">
+      <c r="A1607" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1607" t="s" s="2">
+        <v>3253</v>
+      </c>
+      <c r="C1607" t="s" s="2">
+        <v>3254</v>
+      </c>
+      <c r="D1607" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4880" uniqueCount="3255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4886" uniqueCount="3259">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202604200000</t>
+    <t>202606190000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:06:51-00:00</t>
+    <t>2026-06-19T15:54:56-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2662,7 +2662,7 @@
     <t>GEN-429</t>
   </si>
   <si>
-    <t>Nombre de kits</t>
+    <t>Nombre de kits salivaires</t>
   </si>
   <si>
     <t>GEN-430</t>
@@ -8561,6 +8561,18 @@
   </si>
   <si>
     <t>Entrées/sorties hydro-électrolytiques</t>
+  </si>
+  <si>
+    <t>MED-1351</t>
+  </si>
+  <si>
+    <t>Envoi kit salivaire au CNR</t>
+  </si>
+  <si>
+    <t>MED-1352</t>
+  </si>
+  <si>
+    <t>Envoi autres prélèvements au CNR</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10172,7 +10184,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1607"/>
+  <dimension ref="A1:D1609"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29461,6 +29473,30 @@
       </c>
       <c r="D1607" s="2"/>
     </row>
+    <row r="1608">
+      <c r="A1608" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1608" t="s" s="2">
+        <v>3255</v>
+      </c>
+      <c r="C1608" t="s" s="2">
+        <v>3256</v>
+      </c>
+      <c r="D1608" s="2"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1609" t="s" s="2">
+        <v>3257</v>
+      </c>
+      <c r="C1609" t="s" s="2">
+        <v>3258</v>
+      </c>
+      <c r="D1609" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
